--- a/index.xlsx
+++ b/index.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PEDRO.MATHIAS\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5746AC31-D8DA-4938-A65B-236CF91E063D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2E56CDB-FF84-4539-BA90-3932561168D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -10394,1102 +10394,1102 @@
     <t>Gestão</t>
   </si>
   <si>
-    <t>28/10/2026</t>
-  </si>
-  <si>
-    <t>20/02/2026</t>
-  </si>
-  <si>
-    <t>03/07/2026</t>
-  </si>
-  <si>
-    <t>12/12/2026</t>
-  </si>
-  <si>
-    <t>20/08/2026</t>
-  </si>
-  <si>
-    <t>25/06/2026</t>
-  </si>
-  <si>
-    <t>17/11/2026</t>
-  </si>
-  <si>
-    <t>27/11/2026</t>
-  </si>
-  <si>
-    <t>10/11/2026</t>
-  </si>
-  <si>
-    <t>25/04/2026</t>
-  </si>
-  <si>
-    <t>07/01/2026</t>
-  </si>
-  <si>
-    <t>24/07/2026</t>
-  </si>
-  <si>
-    <t>13/08/2026</t>
-  </si>
-  <si>
-    <t>21/11/2026</t>
-  </si>
-  <si>
-    <t>22/10/2026</t>
-  </si>
-  <si>
-    <t>14/04/2026</t>
-  </si>
-  <si>
-    <t>24/06/2026</t>
-  </si>
-  <si>
-    <t>28/05/2026</t>
-  </si>
-  <si>
-    <t>20/12/2026</t>
-  </si>
-  <si>
-    <t>17/08/2026</t>
-  </si>
-  <si>
-    <t>08/12/2026</t>
-  </si>
-  <si>
-    <t>02/10/2026</t>
-  </si>
-  <si>
-    <t>12/11/2026</t>
-  </si>
-  <si>
-    <t>16/11/2026</t>
-  </si>
-  <si>
-    <t>19/11/2026</t>
-  </si>
-  <si>
-    <t>23/10/2026</t>
-  </si>
-  <si>
-    <t>22/11/2026</t>
-  </si>
-  <si>
-    <t>27/10/2026</t>
-  </si>
-  <si>
-    <t>10/09/2026</t>
-  </si>
-  <si>
-    <t>25/03/2026</t>
-  </si>
-  <si>
-    <t>02/05/2026</t>
-  </si>
-  <si>
-    <t>25/10/2026</t>
-  </si>
-  <si>
-    <t>06/03/2026</t>
-  </si>
-  <si>
-    <t>07/09/2026</t>
-  </si>
-  <si>
-    <t>13/09/2026</t>
-  </si>
-  <si>
-    <t>07/10/2026</t>
-  </si>
-  <si>
-    <t>29/04/2026</t>
-  </si>
-  <si>
-    <t>31/10/2026</t>
-  </si>
-  <si>
-    <t>05/01/2026</t>
-  </si>
-  <si>
-    <t>09/03/2026</t>
-  </si>
-  <si>
-    <t>28/03/2026</t>
-  </si>
-  <si>
-    <t>13/10/2026</t>
-  </si>
-  <si>
-    <t>25/05/2026</t>
-  </si>
-  <si>
-    <t>26/07/2026</t>
-  </si>
-  <si>
-    <t>31/08/2026</t>
-  </si>
-  <si>
-    <t>23/06/2026</t>
-  </si>
-  <si>
-    <t>17/04/2026</t>
-  </si>
-  <si>
-    <t>16/03/2026</t>
-  </si>
-  <si>
-    <t>08/03/2026</t>
-  </si>
-  <si>
-    <t>03/08/2026</t>
-  </si>
-  <si>
-    <t>24/02/2026</t>
-  </si>
-  <si>
-    <t>18/02/2026</t>
-  </si>
-  <si>
-    <t>02/02/2026</t>
-  </si>
-  <si>
-    <t>12/09/2026</t>
-  </si>
-  <si>
-    <t>07/06/2026</t>
-  </si>
-  <si>
-    <t>22/07/2026</t>
-  </si>
-  <si>
-    <t>14/08/2026</t>
-  </si>
-  <si>
-    <t>26/01/2026</t>
-  </si>
-  <si>
-    <t>03/10/2026</t>
-  </si>
-  <si>
-    <t>25/01/2026</t>
-  </si>
-  <si>
-    <t>11/03/2026</t>
-  </si>
-  <si>
-    <t>02/09/2026</t>
-  </si>
-  <si>
-    <t>20/07/2026</t>
-  </si>
-  <si>
-    <t>22/02/2026</t>
-  </si>
-  <si>
-    <t>15/09/2026</t>
-  </si>
-  <si>
-    <t>07/07/2026</t>
-  </si>
-  <si>
-    <t>06/04/2026</t>
-  </si>
-  <si>
-    <t>13/12/2026</t>
-  </si>
-  <si>
-    <t>14/05/2026</t>
-  </si>
-  <si>
-    <t>18/08/2026</t>
-  </si>
-  <si>
-    <t>21/05/2026</t>
-  </si>
-  <si>
-    <t>01/01/2026</t>
-  </si>
-  <si>
-    <t>28/01/2026</t>
-  </si>
-  <si>
-    <t>09/02/2026</t>
-  </si>
-  <si>
-    <t>14/06/2026</t>
-  </si>
-  <si>
-    <t>07/03/2026</t>
-  </si>
-  <si>
-    <t>25/08/2026</t>
-  </si>
-  <si>
-    <t>23/05/2026</t>
-  </si>
-  <si>
-    <t>08/08/2026</t>
-  </si>
-  <si>
-    <t>19/03/2026</t>
-  </si>
-  <si>
-    <t>01/10/2026</t>
-  </si>
-  <si>
-    <t>21/08/2026</t>
-  </si>
-  <si>
-    <t>20/06/2026</t>
-  </si>
-  <si>
-    <t>12/02/2026</t>
-  </si>
-  <si>
-    <t>05/12/2026</t>
-  </si>
-  <si>
-    <t>07/08/2026</t>
-  </si>
-  <si>
-    <t>07/11/2026</t>
-  </si>
-  <si>
-    <t>02/07/2026</t>
-  </si>
-  <si>
-    <t>11/09/2026</t>
-  </si>
-  <si>
-    <t>26/11/2026</t>
-  </si>
-  <si>
-    <t>06/07/2026</t>
-  </si>
-  <si>
-    <t>17/05/2026</t>
-  </si>
-  <si>
-    <t>30/10/2026</t>
-  </si>
-  <si>
-    <t>31/07/2026</t>
-  </si>
-  <si>
-    <t>20/05/2026</t>
-  </si>
-  <si>
-    <t>10/03/2026</t>
-  </si>
-  <si>
-    <t>26/03/2026</t>
-  </si>
-  <si>
-    <t>30/06/2026</t>
-  </si>
-  <si>
-    <t>15/12/2026</t>
-  </si>
-  <si>
-    <t>15/02/2026</t>
-  </si>
-  <si>
-    <t>09/08/2026</t>
-  </si>
-  <si>
-    <t>13/02/2026</t>
-  </si>
-  <si>
-    <t>03/09/2026</t>
-  </si>
-  <si>
-    <t>22/04/2026</t>
-  </si>
-  <si>
-    <t>28/04/2026</t>
-  </si>
-  <si>
-    <t>08/05/2026</t>
-  </si>
-  <si>
-    <t>17/01/2026</t>
-  </si>
-  <si>
-    <t>18/05/2026</t>
-  </si>
-  <si>
-    <t>04/08/2026</t>
-  </si>
-  <si>
-    <t>20/10/2026</t>
-  </si>
-  <si>
-    <t>28/07/2026</t>
-  </si>
-  <si>
-    <t>05/09/2026</t>
-  </si>
-  <si>
-    <t>14/10/2026</t>
-  </si>
-  <si>
-    <t>05/03/2026</t>
-  </si>
-  <si>
-    <t>17/09/2026</t>
-  </si>
-  <si>
-    <t>12/03/2026</t>
-  </si>
-  <si>
-    <t>30/11/2026</t>
-  </si>
-  <si>
-    <t>15/07/2026</t>
-  </si>
-  <si>
-    <t>03/01/2026</t>
-  </si>
-  <si>
-    <t>14/11/2026</t>
-  </si>
-  <si>
-    <t>01/09/2026</t>
-  </si>
-  <si>
-    <t>19/02/2026</t>
-  </si>
-  <si>
-    <t>01/11/2026</t>
-  </si>
-  <si>
-    <t>05/11/2026</t>
-  </si>
-  <si>
-    <t>28/08/2026</t>
-  </si>
-  <si>
-    <t>24/08/2026</t>
-  </si>
-  <si>
-    <t>30/12/2026</t>
-  </si>
-  <si>
-    <t>22/08/2026</t>
-  </si>
-  <si>
-    <t>30/04/2026</t>
-  </si>
-  <si>
-    <t>11/04/2026</t>
-  </si>
-  <si>
-    <t>09/10/2026</t>
-  </si>
-  <si>
-    <t>28/06/2026</t>
-  </si>
-  <si>
-    <t>30/05/2026</t>
-  </si>
-  <si>
-    <t>08/09/2026</t>
-  </si>
-  <si>
-    <t>11/06/2026</t>
-  </si>
-  <si>
-    <t>23/02/2026</t>
-  </si>
-  <si>
-    <t>26/06/2026</t>
-  </si>
-  <si>
-    <t>24/09/2026</t>
-  </si>
-  <si>
-    <t>02/06/2026</t>
-  </si>
-  <si>
-    <t>15/11/2026</t>
-  </si>
-  <si>
-    <t>27/06/2026</t>
-  </si>
-  <si>
-    <t>15/08/2026</t>
-  </si>
-  <si>
-    <t>23/11/2026</t>
-  </si>
-  <si>
-    <t>10/05/2026</t>
-  </si>
-  <si>
-    <t>21/04/2026</t>
-  </si>
-  <si>
-    <t>16/05/2026</t>
-  </si>
-  <si>
-    <t>15/10/2026</t>
-  </si>
-  <si>
-    <t>28/12/2026</t>
-  </si>
-  <si>
-    <t>17/02/2026</t>
-  </si>
-  <si>
-    <t>30/09/2026</t>
-  </si>
-  <si>
-    <t>21/06/2026</t>
-  </si>
-  <si>
-    <t>18/04/2026</t>
-  </si>
-  <si>
-    <t>01/12/2026</t>
-  </si>
-  <si>
-    <t>07/02/2026</t>
-  </si>
-  <si>
-    <t>26/08/2026</t>
-  </si>
-  <si>
-    <t>29/08/2026</t>
-  </si>
-  <si>
-    <t>18/11/2026</t>
-  </si>
-  <si>
-    <t>15/05/2026</t>
-  </si>
-  <si>
-    <t>27/01/2026</t>
-  </si>
-  <si>
-    <t>23/04/2026</t>
-  </si>
-  <si>
-    <t>15/06/2026</t>
-  </si>
-  <si>
-    <t>20/04/2026</t>
-  </si>
-  <si>
-    <t>19/06/2026</t>
-  </si>
-  <si>
-    <t>26/12/2026</t>
-  </si>
-  <si>
-    <t>24/10/2026</t>
-  </si>
-  <si>
-    <t>06/08/2026</t>
-  </si>
-  <si>
-    <t>30/08/2026</t>
-  </si>
-  <si>
-    <t>11/10/2026</t>
-  </si>
-  <si>
-    <t>05/02/2026</t>
-  </si>
-  <si>
-    <t>01/02/2026</t>
-  </si>
-  <si>
-    <t>11/05/2026</t>
-  </si>
-  <si>
-    <t>07/12/2026</t>
-  </si>
-  <si>
-    <t>08/01/2026</t>
-  </si>
-  <si>
-    <t>11/07/2026</t>
-  </si>
-  <si>
-    <t>26/09/2026</t>
-  </si>
-  <si>
-    <t>10/06/2026</t>
-  </si>
-  <si>
-    <t>10/01/2026</t>
-  </si>
-  <si>
-    <t>02/04/2026</t>
-  </si>
-  <si>
-    <t>15/01/2026</t>
-  </si>
-  <si>
-    <t>14/09/2026</t>
-  </si>
-  <si>
-    <t>05/04/2026</t>
-  </si>
-  <si>
-    <t>29/10/2026</t>
-  </si>
-  <si>
-    <t>22/01/2026</t>
-  </si>
-  <si>
-    <t>12/01/2026</t>
-  </si>
-  <si>
-    <t>11/08/2026</t>
-  </si>
-  <si>
-    <t>11/12/2026</t>
-  </si>
-  <si>
-    <t>30/03/2026</t>
-  </si>
-  <si>
-    <t>17/07/2026</t>
-  </si>
-  <si>
-    <t>16/02/2026</t>
-  </si>
-  <si>
-    <t>22/06/2026</t>
-  </si>
-  <si>
-    <t>30/07/2026</t>
-  </si>
-  <si>
-    <t>24/04/2026</t>
-  </si>
-  <si>
-    <t>21/09/2026</t>
-  </si>
-  <si>
-    <t>14/02/2026</t>
-  </si>
-  <si>
-    <t>21/12/2026</t>
-  </si>
-  <si>
-    <t>18/10/2026</t>
-  </si>
-  <si>
-    <t>29/07/2026</t>
-  </si>
-  <si>
-    <t>09/07/2026</t>
-  </si>
-  <si>
-    <t>04/05/2026</t>
-  </si>
-  <si>
-    <t>17/03/2026</t>
-  </si>
-  <si>
-    <t>14/07/2026</t>
-  </si>
-  <si>
-    <t>16/12/2026</t>
-  </si>
-  <si>
-    <t>11/01/2026</t>
-  </si>
-  <si>
-    <t>18/01/2026</t>
-  </si>
-  <si>
-    <t>07/05/2026</t>
-  </si>
-  <si>
-    <t>18/07/2026</t>
-  </si>
-  <si>
-    <t>06/09/2026</t>
-  </si>
-  <si>
-    <t>12/04/2026</t>
-  </si>
-  <si>
-    <t>24/11/2026</t>
-  </si>
-  <si>
-    <t>21/10/2026</t>
-  </si>
-  <si>
-    <t>19/07/2026</t>
-  </si>
-  <si>
-    <t>01/03/2026</t>
-  </si>
-  <si>
-    <t>05/10/2026</t>
-  </si>
-  <si>
-    <t>21/01/2026</t>
-  </si>
-  <si>
-    <t>12/05/2026</t>
-  </si>
-  <si>
-    <t>26/05/2026</t>
-  </si>
-  <si>
-    <t>03/02/2026</t>
-  </si>
-  <si>
-    <t>22/03/2026</t>
-  </si>
-  <si>
-    <t>13/05/2026</t>
-  </si>
-  <si>
-    <t>10/10/2026</t>
-  </si>
-  <si>
-    <t>01/07/2026</t>
-  </si>
-  <si>
-    <t>31/12/2026</t>
-  </si>
-  <si>
-    <t>10/08/2026</t>
-  </si>
-  <si>
-    <t>26/04/2026</t>
-  </si>
-  <si>
-    <t>13/06/2026</t>
-  </si>
-  <si>
-    <t>17/06/2026</t>
-  </si>
-  <si>
-    <t>16/07/2026</t>
-  </si>
-  <si>
-    <t>08/04/2026</t>
-  </si>
-  <si>
-    <t>25/02/2026</t>
-  </si>
-  <si>
-    <t>05/08/2026</t>
-  </si>
-  <si>
-    <t>12/08/2026</t>
-  </si>
-  <si>
-    <t>09/11/2026</t>
-  </si>
-  <si>
-    <t>19/04/2026</t>
-  </si>
-  <si>
-    <t>02/08/2026</t>
-  </si>
-  <si>
-    <t>03/05/2026</t>
-  </si>
-  <si>
-    <t>14/03/2026</t>
-  </si>
-  <si>
-    <t>06/05/2026</t>
-  </si>
-  <si>
-    <t>08/06/2026</t>
-  </si>
-  <si>
-    <t>02/01/2026</t>
-  </si>
-  <si>
-    <t>28/09/2026</t>
-  </si>
-  <si>
-    <t>05/06/2026</t>
-  </si>
-  <si>
-    <t>13/11/2026</t>
-  </si>
-  <si>
-    <t>04/01/2026</t>
-  </si>
-  <si>
-    <t>06/01/2026</t>
-  </si>
-  <si>
-    <t>29/03/2026</t>
-  </si>
-  <si>
-    <t>13/03/2026</t>
-  </si>
-  <si>
-    <t>21/07/2026</t>
-  </si>
-  <si>
-    <t>13/07/2026</t>
-  </si>
-  <si>
-    <t>03/03/2026</t>
-  </si>
-  <si>
-    <t>18/12/2026</t>
-  </si>
-  <si>
-    <t>20/03/2026</t>
-  </si>
-  <si>
-    <t>16/09/2026</t>
-  </si>
-  <si>
-    <t>27/12/2026</t>
-  </si>
-  <si>
-    <t>27/04/2026</t>
-  </si>
-  <si>
-    <t>09/12/2026</t>
-  </si>
-  <si>
-    <t>23/01/2026</t>
-  </si>
-  <si>
-    <t>27/03/2026</t>
-  </si>
-  <si>
-    <t>23/07/2026</t>
-  </si>
-  <si>
-    <t>29/01/2026</t>
-  </si>
-  <si>
-    <t>28/02/2026</t>
-  </si>
-  <si>
-    <t>20/09/2026</t>
-  </si>
-  <si>
-    <t>12/07/2026</t>
-  </si>
-  <si>
-    <t>19/05/2026</t>
-  </si>
-  <si>
-    <t>25/07/2026</t>
-  </si>
-  <si>
-    <t>04/10/2026</t>
-  </si>
-  <si>
-    <t>30/01/2026</t>
-  </si>
-  <si>
-    <t>09/04/2026</t>
-  </si>
-  <si>
-    <t>08/10/2026</t>
-  </si>
-  <si>
-    <t>24/12/2026</t>
-  </si>
-  <si>
-    <t>09/05/2026</t>
-  </si>
-  <si>
-    <t>18/09/2026</t>
-  </si>
-  <si>
-    <t>22/05/2026</t>
-  </si>
-  <si>
-    <t>15/04/2026</t>
-  </si>
-  <si>
-    <t>06/10/2026</t>
-  </si>
-  <si>
-    <t>27/09/2026</t>
-  </si>
-  <si>
-    <t>22/09/2026</t>
-  </si>
-  <si>
-    <t>23/12/2026</t>
-  </si>
-  <si>
-    <t>19/08/2026</t>
-  </si>
-  <si>
-    <t>02/11/2026</t>
-  </si>
-  <si>
-    <t>18/03/2026</t>
-  </si>
-  <si>
-    <t>10/04/2026</t>
-  </si>
-  <si>
-    <t>13/04/2026</t>
-  </si>
-  <si>
-    <t>23/03/2026</t>
-  </si>
-  <si>
-    <t>19/09/2026</t>
-  </si>
-  <si>
-    <t>27/05/2026</t>
-  </si>
-  <si>
-    <t>08/07/2026</t>
-  </si>
-  <si>
-    <t>04/12/2026</t>
-  </si>
-  <si>
-    <t>20/11/2026</t>
-  </si>
-  <si>
-    <t>12/06/2026</t>
-  </si>
-  <si>
-    <t>16/01/2026</t>
-  </si>
-  <si>
-    <t>10/02/2026</t>
-  </si>
-  <si>
-    <t>04/03/2026</t>
-  </si>
-  <si>
-    <t>23/08/2026</t>
-  </si>
-  <si>
-    <t>16/10/2026</t>
-  </si>
-  <si>
-    <t>27/02/2026</t>
-  </si>
-  <si>
-    <t>08/11/2026</t>
-  </si>
-  <si>
-    <t>03/04/2026</t>
-  </si>
-  <si>
-    <t>25/11/2026</t>
-  </si>
-  <si>
-    <t>15/03/2026</t>
-  </si>
-  <si>
-    <t>31/03/2026</t>
-  </si>
-  <si>
-    <t>29/11/2026</t>
-  </si>
-  <si>
-    <t>06/02/2026</t>
-  </si>
-  <si>
-    <t>09/06/2026</t>
-  </si>
-  <si>
-    <t>22/12/2026</t>
-  </si>
-  <si>
-    <t>29/05/2026</t>
-  </si>
-  <si>
-    <t>09/09/2026</t>
-  </si>
-  <si>
-    <t>14/12/2026</t>
-  </si>
-  <si>
-    <t>16/04/2026</t>
-  </si>
-  <si>
-    <t>13/01/2026</t>
-  </si>
-  <si>
-    <t>08/02/2026</t>
-  </si>
-  <si>
-    <t>06/12/2026</t>
-  </si>
-  <si>
-    <t>01/08/2026</t>
-  </si>
-  <si>
-    <t>06/06/2026</t>
-  </si>
-  <si>
-    <t>11/11/2026</t>
-  </si>
-  <si>
-    <t>09/01/2026</t>
-  </si>
-  <si>
-    <t>20/01/2026</t>
-  </si>
-  <si>
-    <t>05/05/2026</t>
-  </si>
-  <si>
-    <t>04/07/2026</t>
-  </si>
-  <si>
-    <t>04/11/2026</t>
-  </si>
-  <si>
-    <t>23/09/2026</t>
-  </si>
-  <si>
-    <t>27/07/2026</t>
-  </si>
-  <si>
-    <t>03/06/2026</t>
-  </si>
-  <si>
-    <t>10/12/2026</t>
-  </si>
-  <si>
-    <t>04/04/2026</t>
-  </si>
-  <si>
-    <t>29/06/2026</t>
-  </si>
-  <si>
-    <t>16/08/2026</t>
-  </si>
-  <si>
-    <t>27/08/2026</t>
-  </si>
-  <si>
-    <t>04/06/2026</t>
-  </si>
-  <si>
-    <t>14/01/2026</t>
-  </si>
-  <si>
-    <t>10/07/2026</t>
-  </si>
-  <si>
-    <t>31/05/2026</t>
-  </si>
-  <si>
-    <t>03/12/2026</t>
-  </si>
-  <si>
-    <t>26/10/2026</t>
-  </si>
-  <si>
-    <t>04/09/2026</t>
-  </si>
-  <si>
-    <t>17/10/2026</t>
-  </si>
-  <si>
-    <t>25/09/2026</t>
-  </si>
-  <si>
-    <t>31/01/2026</t>
-  </si>
-  <si>
-    <t>24/05/2026</t>
-  </si>
-  <si>
-    <t>28/11/2026</t>
-  </si>
-  <si>
-    <t>03/11/2026</t>
-  </si>
-  <si>
-    <t>21/02/2026</t>
-  </si>
-  <si>
-    <t>05/07/2026</t>
-  </si>
-  <si>
-    <t>01/04/2026</t>
-  </si>
-  <si>
-    <t>11/02/2026</t>
-  </si>
-  <si>
-    <t>17/12/2026</t>
-  </si>
-  <si>
-    <t>19/01/2026</t>
-  </si>
-  <si>
-    <t>26/02/2026</t>
-  </si>
-  <si>
-    <t>18/06/2026</t>
-  </si>
-  <si>
-    <t>04/02/2026</t>
-  </si>
-  <si>
-    <t>29/09/2026</t>
-  </si>
-  <si>
-    <t>24/01/2026</t>
-  </si>
-  <si>
-    <t>24/03/2026</t>
-  </si>
-  <si>
-    <t>02/12/2026</t>
-  </si>
-  <si>
-    <t>01/05/2026</t>
-  </si>
-  <si>
-    <t>01/06/2026</t>
-  </si>
-  <si>
-    <t>21/03/2026</t>
-  </si>
-  <si>
-    <t>19/12/2026</t>
-  </si>
-  <si>
-    <t>02/03/2026</t>
-  </si>
-  <si>
-    <t>25/12/2026</t>
-  </si>
-  <si>
-    <t>06/11/2026</t>
-  </si>
-  <si>
-    <t>29/02/2026</t>
-  </si>
-  <si>
-    <t>12/10/2026</t>
-  </si>
-  <si>
-    <t>19/10/2026</t>
-  </si>
-  <si>
-    <t>29/12/2026</t>
-  </si>
-  <si>
-    <t>16/06/2026</t>
-  </si>
-  <si>
-    <t>07/04/2026</t>
+    <t>28/10</t>
+  </si>
+  <si>
+    <t>20/02</t>
+  </si>
+  <si>
+    <t>03/07</t>
+  </si>
+  <si>
+    <t>12/12</t>
+  </si>
+  <si>
+    <t>20/08</t>
+  </si>
+  <si>
+    <t>25/06</t>
+  </si>
+  <si>
+    <t>17/11</t>
+  </si>
+  <si>
+    <t>27/11</t>
+  </si>
+  <si>
+    <t>10/11</t>
+  </si>
+  <si>
+    <t>25/04</t>
+  </si>
+  <si>
+    <t>07/01</t>
+  </si>
+  <si>
+    <t>24/07</t>
+  </si>
+  <si>
+    <t>13/08</t>
+  </si>
+  <si>
+    <t>21/11</t>
+  </si>
+  <si>
+    <t>22/10</t>
+  </si>
+  <si>
+    <t>14/04</t>
+  </si>
+  <si>
+    <t>24/06</t>
+  </si>
+  <si>
+    <t>28/05</t>
+  </si>
+  <si>
+    <t>20/12</t>
+  </si>
+  <si>
+    <t>17/08</t>
+  </si>
+  <si>
+    <t>08/12</t>
+  </si>
+  <si>
+    <t>02/10</t>
+  </si>
+  <si>
+    <t>12/11</t>
+  </si>
+  <si>
+    <t>16/11</t>
+  </si>
+  <si>
+    <t>19/11</t>
+  </si>
+  <si>
+    <t>23/10</t>
+  </si>
+  <si>
+    <t>22/11</t>
+  </si>
+  <si>
+    <t>27/10</t>
+  </si>
+  <si>
+    <t>10/09</t>
+  </si>
+  <si>
+    <t>25/03</t>
+  </si>
+  <si>
+    <t>02/05</t>
+  </si>
+  <si>
+    <t>25/10</t>
+  </si>
+  <si>
+    <t>06/03</t>
+  </si>
+  <si>
+    <t>07/09</t>
+  </si>
+  <si>
+    <t>13/09</t>
+  </si>
+  <si>
+    <t>07/10</t>
+  </si>
+  <si>
+    <t>29/04</t>
+  </si>
+  <si>
+    <t>31/10</t>
+  </si>
+  <si>
+    <t>05/01</t>
+  </si>
+  <si>
+    <t>09/03</t>
+  </si>
+  <si>
+    <t>28/03</t>
+  </si>
+  <si>
+    <t>13/10</t>
+  </si>
+  <si>
+    <t>25/05</t>
+  </si>
+  <si>
+    <t>26/07</t>
+  </si>
+  <si>
+    <t>31/08</t>
+  </si>
+  <si>
+    <t>23/06</t>
+  </si>
+  <si>
+    <t>17/04</t>
+  </si>
+  <si>
+    <t>16/03</t>
+  </si>
+  <si>
+    <t>08/03</t>
+  </si>
+  <si>
+    <t>03/08</t>
+  </si>
+  <si>
+    <t>24/02</t>
+  </si>
+  <si>
+    <t>18/02</t>
+  </si>
+  <si>
+    <t>02/02</t>
+  </si>
+  <si>
+    <t>12/09</t>
+  </si>
+  <si>
+    <t>07/06</t>
+  </si>
+  <si>
+    <t>22/07</t>
+  </si>
+  <si>
+    <t>14/08</t>
+  </si>
+  <si>
+    <t>26/01</t>
+  </si>
+  <si>
+    <t>03/10</t>
+  </si>
+  <si>
+    <t>25/01</t>
+  </si>
+  <si>
+    <t>11/03</t>
+  </si>
+  <si>
+    <t>02/09</t>
+  </si>
+  <si>
+    <t>20/07</t>
+  </si>
+  <si>
+    <t>22/02</t>
+  </si>
+  <si>
+    <t>15/09</t>
+  </si>
+  <si>
+    <t>07/07</t>
+  </si>
+  <si>
+    <t>06/04</t>
+  </si>
+  <si>
+    <t>13/12</t>
+  </si>
+  <si>
+    <t>14/05</t>
+  </si>
+  <si>
+    <t>18/08</t>
+  </si>
+  <si>
+    <t>21/05</t>
+  </si>
+  <si>
+    <t>01/01</t>
+  </si>
+  <si>
+    <t>28/01</t>
+  </si>
+  <si>
+    <t>09/02</t>
+  </si>
+  <si>
+    <t>14/06</t>
+  </si>
+  <si>
+    <t>07/03</t>
+  </si>
+  <si>
+    <t>25/08</t>
+  </si>
+  <si>
+    <t>23/05</t>
+  </si>
+  <si>
+    <t>08/08</t>
+  </si>
+  <si>
+    <t>19/03</t>
+  </si>
+  <si>
+    <t>01/10</t>
+  </si>
+  <si>
+    <t>21/08</t>
+  </si>
+  <si>
+    <t>20/06</t>
+  </si>
+  <si>
+    <t>12/02</t>
+  </si>
+  <si>
+    <t>05/12</t>
+  </si>
+  <si>
+    <t>07/08</t>
+  </si>
+  <si>
+    <t>07/11</t>
+  </si>
+  <si>
+    <t>02/07</t>
+  </si>
+  <si>
+    <t>11/09</t>
+  </si>
+  <si>
+    <t>26/11</t>
+  </si>
+  <si>
+    <t>06/07</t>
+  </si>
+  <si>
+    <t>17/05</t>
+  </si>
+  <si>
+    <t>30/10</t>
+  </si>
+  <si>
+    <t>31/07</t>
+  </si>
+  <si>
+    <t>20/05</t>
+  </si>
+  <si>
+    <t>10/03</t>
+  </si>
+  <si>
+    <t>26/03</t>
+  </si>
+  <si>
+    <t>30/06</t>
+  </si>
+  <si>
+    <t>15/12</t>
+  </si>
+  <si>
+    <t>15/02</t>
+  </si>
+  <si>
+    <t>09/08</t>
+  </si>
+  <si>
+    <t>13/02</t>
+  </si>
+  <si>
+    <t>03/09</t>
+  </si>
+  <si>
+    <t>22/04</t>
+  </si>
+  <si>
+    <t>28/04</t>
+  </si>
+  <si>
+    <t>08/05</t>
+  </si>
+  <si>
+    <t>17/01</t>
+  </si>
+  <si>
+    <t>18/05</t>
+  </si>
+  <si>
+    <t>04/08</t>
+  </si>
+  <si>
+    <t>20/10</t>
+  </si>
+  <si>
+    <t>28/07</t>
+  </si>
+  <si>
+    <t>05/09</t>
+  </si>
+  <si>
+    <t>14/10</t>
+  </si>
+  <si>
+    <t>05/03</t>
+  </si>
+  <si>
+    <t>17/09</t>
+  </si>
+  <si>
+    <t>12/03</t>
+  </si>
+  <si>
+    <t>30/11</t>
+  </si>
+  <si>
+    <t>15/07</t>
+  </si>
+  <si>
+    <t>03/01</t>
+  </si>
+  <si>
+    <t>14/11</t>
+  </si>
+  <si>
+    <t>01/09</t>
+  </si>
+  <si>
+    <t>19/02</t>
+  </si>
+  <si>
+    <t>01/11</t>
+  </si>
+  <si>
+    <t>05/11</t>
+  </si>
+  <si>
+    <t>28/08</t>
+  </si>
+  <si>
+    <t>24/08</t>
+  </si>
+  <si>
+    <t>30/12</t>
+  </si>
+  <si>
+    <t>22/08</t>
+  </si>
+  <si>
+    <t>30/04</t>
+  </si>
+  <si>
+    <t>11/04</t>
+  </si>
+  <si>
+    <t>09/10</t>
+  </si>
+  <si>
+    <t>28/06</t>
+  </si>
+  <si>
+    <t>30/05</t>
+  </si>
+  <si>
+    <t>08/09</t>
+  </si>
+  <si>
+    <t>11/06</t>
+  </si>
+  <si>
+    <t>23/02</t>
+  </si>
+  <si>
+    <t>26/06</t>
+  </si>
+  <si>
+    <t>24/09</t>
+  </si>
+  <si>
+    <t>02/06</t>
+  </si>
+  <si>
+    <t>15/11</t>
+  </si>
+  <si>
+    <t>27/06</t>
+  </si>
+  <si>
+    <t>15/08</t>
+  </si>
+  <si>
+    <t>23/11</t>
+  </si>
+  <si>
+    <t>10/05</t>
+  </si>
+  <si>
+    <t>21/04</t>
+  </si>
+  <si>
+    <t>16/05</t>
+  </si>
+  <si>
+    <t>15/10</t>
+  </si>
+  <si>
+    <t>28/12</t>
+  </si>
+  <si>
+    <t>17/02</t>
+  </si>
+  <si>
+    <t>30/09</t>
+  </si>
+  <si>
+    <t>21/06</t>
+  </si>
+  <si>
+    <t>18/04</t>
+  </si>
+  <si>
+    <t>01/12</t>
+  </si>
+  <si>
+    <t>07/02</t>
+  </si>
+  <si>
+    <t>26/08</t>
+  </si>
+  <si>
+    <t>29/08</t>
+  </si>
+  <si>
+    <t>18/11</t>
+  </si>
+  <si>
+    <t>15/05</t>
+  </si>
+  <si>
+    <t>27/01</t>
+  </si>
+  <si>
+    <t>23/04</t>
+  </si>
+  <si>
+    <t>15/06</t>
+  </si>
+  <si>
+    <t>20/04</t>
+  </si>
+  <si>
+    <t>19/06</t>
+  </si>
+  <si>
+    <t>26/12</t>
+  </si>
+  <si>
+    <t>24/10</t>
+  </si>
+  <si>
+    <t>06/08</t>
+  </si>
+  <si>
+    <t>30/08</t>
+  </si>
+  <si>
+    <t>11/10</t>
+  </si>
+  <si>
+    <t>05/02</t>
+  </si>
+  <si>
+    <t>01/02</t>
+  </si>
+  <si>
+    <t>11/05</t>
+  </si>
+  <si>
+    <t>07/12</t>
+  </si>
+  <si>
+    <t>08/01</t>
+  </si>
+  <si>
+    <t>11/07</t>
+  </si>
+  <si>
+    <t>26/09</t>
+  </si>
+  <si>
+    <t>10/06</t>
+  </si>
+  <si>
+    <t>10/01</t>
+  </si>
+  <si>
+    <t>02/04</t>
+  </si>
+  <si>
+    <t>15/01</t>
+  </si>
+  <si>
+    <t>14/09</t>
+  </si>
+  <si>
+    <t>05/04</t>
+  </si>
+  <si>
+    <t>29/10</t>
+  </si>
+  <si>
+    <t>22/01</t>
+  </si>
+  <si>
+    <t>12/01</t>
+  </si>
+  <si>
+    <t>11/08</t>
+  </si>
+  <si>
+    <t>11/12</t>
+  </si>
+  <si>
+    <t>30/03</t>
+  </si>
+  <si>
+    <t>17/07</t>
+  </si>
+  <si>
+    <t>16/02</t>
+  </si>
+  <si>
+    <t>22/06</t>
+  </si>
+  <si>
+    <t>30/07</t>
+  </si>
+  <si>
+    <t>24/04</t>
+  </si>
+  <si>
+    <t>21/09</t>
+  </si>
+  <si>
+    <t>14/02</t>
+  </si>
+  <si>
+    <t>21/12</t>
+  </si>
+  <si>
+    <t>18/10</t>
+  </si>
+  <si>
+    <t>29/07</t>
+  </si>
+  <si>
+    <t>09/07</t>
+  </si>
+  <si>
+    <t>04/05</t>
+  </si>
+  <si>
+    <t>17/03</t>
+  </si>
+  <si>
+    <t>14/07</t>
+  </si>
+  <si>
+    <t>16/12</t>
+  </si>
+  <si>
+    <t>11/01</t>
+  </si>
+  <si>
+    <t>18/01</t>
+  </si>
+  <si>
+    <t>07/05</t>
+  </si>
+  <si>
+    <t>18/07</t>
+  </si>
+  <si>
+    <t>06/09</t>
+  </si>
+  <si>
+    <t>12/04</t>
+  </si>
+  <si>
+    <t>24/11</t>
+  </si>
+  <si>
+    <t>21/10</t>
+  </si>
+  <si>
+    <t>19/07</t>
+  </si>
+  <si>
+    <t>01/03</t>
+  </si>
+  <si>
+    <t>05/10</t>
+  </si>
+  <si>
+    <t>21/01</t>
+  </si>
+  <si>
+    <t>12/05</t>
+  </si>
+  <si>
+    <t>26/05</t>
+  </si>
+  <si>
+    <t>03/02</t>
+  </si>
+  <si>
+    <t>22/03</t>
+  </si>
+  <si>
+    <t>13/05</t>
+  </si>
+  <si>
+    <t>10/10</t>
+  </si>
+  <si>
+    <t>01/07</t>
+  </si>
+  <si>
+    <t>31/12</t>
+  </si>
+  <si>
+    <t>10/08</t>
+  </si>
+  <si>
+    <t>26/04</t>
+  </si>
+  <si>
+    <t>13/06</t>
+  </si>
+  <si>
+    <t>17/06</t>
+  </si>
+  <si>
+    <t>16/07</t>
+  </si>
+  <si>
+    <t>08/04</t>
+  </si>
+  <si>
+    <t>25/02</t>
+  </si>
+  <si>
+    <t>05/08</t>
+  </si>
+  <si>
+    <t>12/08</t>
+  </si>
+  <si>
+    <t>09/11</t>
+  </si>
+  <si>
+    <t>19/04</t>
+  </si>
+  <si>
+    <t>02/08</t>
+  </si>
+  <si>
+    <t>03/05</t>
+  </si>
+  <si>
+    <t>14/03</t>
+  </si>
+  <si>
+    <t>06/05</t>
+  </si>
+  <si>
+    <t>08/06</t>
+  </si>
+  <si>
+    <t>02/01</t>
+  </si>
+  <si>
+    <t>28/09</t>
+  </si>
+  <si>
+    <t>05/06</t>
+  </si>
+  <si>
+    <t>13/11</t>
+  </si>
+  <si>
+    <t>04/01</t>
+  </si>
+  <si>
+    <t>06/01</t>
+  </si>
+  <si>
+    <t>29/03</t>
+  </si>
+  <si>
+    <t>13/03</t>
+  </si>
+  <si>
+    <t>21/07</t>
+  </si>
+  <si>
+    <t>13/07</t>
+  </si>
+  <si>
+    <t>03/03</t>
+  </si>
+  <si>
+    <t>18/12</t>
+  </si>
+  <si>
+    <t>20/03</t>
+  </si>
+  <si>
+    <t>16/09</t>
+  </si>
+  <si>
+    <t>27/12</t>
+  </si>
+  <si>
+    <t>27/04</t>
+  </si>
+  <si>
+    <t>09/12</t>
+  </si>
+  <si>
+    <t>23/01</t>
+  </si>
+  <si>
+    <t>27/03</t>
+  </si>
+  <si>
+    <t>23/07</t>
+  </si>
+  <si>
+    <t>29/01</t>
+  </si>
+  <si>
+    <t>28/02</t>
+  </si>
+  <si>
+    <t>20/09</t>
+  </si>
+  <si>
+    <t>12/07</t>
+  </si>
+  <si>
+    <t>19/05</t>
+  </si>
+  <si>
+    <t>25/07</t>
+  </si>
+  <si>
+    <t>04/10</t>
+  </si>
+  <si>
+    <t>30/01</t>
+  </si>
+  <si>
+    <t>09/04</t>
+  </si>
+  <si>
+    <t>08/10</t>
+  </si>
+  <si>
+    <t>24/12</t>
+  </si>
+  <si>
+    <t>09/05</t>
+  </si>
+  <si>
+    <t>18/09</t>
+  </si>
+  <si>
+    <t>22/05</t>
+  </si>
+  <si>
+    <t>15/04</t>
+  </si>
+  <si>
+    <t>06/10</t>
+  </si>
+  <si>
+    <t>27/09</t>
+  </si>
+  <si>
+    <t>22/09</t>
+  </si>
+  <si>
+    <t>23/12</t>
+  </si>
+  <si>
+    <t>19/08</t>
+  </si>
+  <si>
+    <t>02/11</t>
+  </si>
+  <si>
+    <t>18/03</t>
+  </si>
+  <si>
+    <t>10/04</t>
+  </si>
+  <si>
+    <t>13/04</t>
+  </si>
+  <si>
+    <t>23/03</t>
+  </si>
+  <si>
+    <t>19/09</t>
+  </si>
+  <si>
+    <t>27/05</t>
+  </si>
+  <si>
+    <t>08/07</t>
+  </si>
+  <si>
+    <t>04/12</t>
+  </si>
+  <si>
+    <t>20/11</t>
+  </si>
+  <si>
+    <t>12/06</t>
+  </si>
+  <si>
+    <t>16/01</t>
+  </si>
+  <si>
+    <t>10/02</t>
+  </si>
+  <si>
+    <t>04/03</t>
+  </si>
+  <si>
+    <t>23/08</t>
+  </si>
+  <si>
+    <t>16/10</t>
+  </si>
+  <si>
+    <t>27/02</t>
+  </si>
+  <si>
+    <t>08/11</t>
+  </si>
+  <si>
+    <t>03/04</t>
+  </si>
+  <si>
+    <t>25/11</t>
+  </si>
+  <si>
+    <t>15/03</t>
+  </si>
+  <si>
+    <t>31/03</t>
+  </si>
+  <si>
+    <t>29/11</t>
+  </si>
+  <si>
+    <t>06/02</t>
+  </si>
+  <si>
+    <t>09/06</t>
+  </si>
+  <si>
+    <t>22/12</t>
+  </si>
+  <si>
+    <t>29/05</t>
+  </si>
+  <si>
+    <t>09/09</t>
+  </si>
+  <si>
+    <t>14/12</t>
+  </si>
+  <si>
+    <t>16/04</t>
+  </si>
+  <si>
+    <t>13/01</t>
+  </si>
+  <si>
+    <t>08/02</t>
+  </si>
+  <si>
+    <t>06/12</t>
+  </si>
+  <si>
+    <t>01/08</t>
+  </si>
+  <si>
+    <t>06/06</t>
+  </si>
+  <si>
+    <t>11/11</t>
+  </si>
+  <si>
+    <t>09/01</t>
+  </si>
+  <si>
+    <t>20/01</t>
+  </si>
+  <si>
+    <t>05/05</t>
+  </si>
+  <si>
+    <t>04/07</t>
+  </si>
+  <si>
+    <t>04/11</t>
+  </si>
+  <si>
+    <t>23/09</t>
+  </si>
+  <si>
+    <t>27/07</t>
+  </si>
+  <si>
+    <t>03/06</t>
+  </si>
+  <si>
+    <t>10/12</t>
+  </si>
+  <si>
+    <t>04/04</t>
+  </si>
+  <si>
+    <t>29/06</t>
+  </si>
+  <si>
+    <t>16/08</t>
+  </si>
+  <si>
+    <t>27/08</t>
+  </si>
+  <si>
+    <t>04/06</t>
+  </si>
+  <si>
+    <t>14/01</t>
+  </si>
+  <si>
+    <t>10/07</t>
+  </si>
+  <si>
+    <t>31/05</t>
+  </si>
+  <si>
+    <t>03/12</t>
+  </si>
+  <si>
+    <t>26/10</t>
+  </si>
+  <si>
+    <t>04/09</t>
+  </si>
+  <si>
+    <t>17/10</t>
+  </si>
+  <si>
+    <t>25/09</t>
+  </si>
+  <si>
+    <t>31/01</t>
+  </si>
+  <si>
+    <t>24/05</t>
+  </si>
+  <si>
+    <t>28/11</t>
+  </si>
+  <si>
+    <t>03/11</t>
+  </si>
+  <si>
+    <t>21/02</t>
+  </si>
+  <si>
+    <t>05/07</t>
+  </si>
+  <si>
+    <t>01/04</t>
+  </si>
+  <si>
+    <t>11/02</t>
+  </si>
+  <si>
+    <t>17/12</t>
+  </si>
+  <si>
+    <t>19/01</t>
+  </si>
+  <si>
+    <t>26/02</t>
+  </si>
+  <si>
+    <t>18/06</t>
+  </si>
+  <si>
+    <t>04/02</t>
+  </si>
+  <si>
+    <t>29/09</t>
+  </si>
+  <si>
+    <t>24/01</t>
+  </si>
+  <si>
+    <t>24/03</t>
+  </si>
+  <si>
+    <t>02/12</t>
+  </si>
+  <si>
+    <t>01/05</t>
+  </si>
+  <si>
+    <t>01/06</t>
+  </si>
+  <si>
+    <t>21/03</t>
+  </si>
+  <si>
+    <t>19/12</t>
+  </si>
+  <si>
+    <t>02/03</t>
+  </si>
+  <si>
+    <t>25/12</t>
+  </si>
+  <si>
+    <t>06/11</t>
+  </si>
+  <si>
+    <t>29/02</t>
+  </si>
+  <si>
+    <t>12/10</t>
+  </si>
+  <si>
+    <t>19/10</t>
+  </si>
+  <si>
+    <t>29/12</t>
+  </si>
+  <si>
+    <t>16/06</t>
+  </si>
+  <si>
+    <t>07/04</t>
   </si>
 </sst>
 </file>

--- a/index.xlsx
+++ b/index.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PEDRO.MATHIAS\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2E56CDB-FF84-4539-BA90-3932561168D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C51A5FB-6823-4D9D-AAAB-36DBB6FCC3C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -11524,7 +11524,7 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -11879,7 +11879,7 @@
       <c r="C1" t="s">
         <v>3450</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>3451</v>
       </c>
       <c r="E1" t="s">
